--- a/05_交付物/通俗细分版_2026-08-07/05_编程数学数据分析和可视化/00_大分类总览.xlsx
+++ b/05_交付物/通俗细分版_2026-08-07/05_编程数学数据分析和可视化/00_大分类总览.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="rId4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI技能清单" sheetId="2" r:id="rId5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类统计" sheetId="3" r:id="rId6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源清单" sheetId="4" r:id="rId7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R491eb27989c7499a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI技能清单" sheetId="2" r:id="R2d7b08b6edb94cbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类统计" sheetId="3" r:id="R7d4dad11b55b42d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源清单" sheetId="4" r:id="R39604f80ebe24654"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4684,119 +4684,119 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:hyperlinks>
-    <x:hyperlink ref="U5" r:id="rId4"/>
-    <x:hyperlink ref="V5" r:id="rId28"/>
-    <x:hyperlink ref="U6" r:id="rId2"/>
-    <x:hyperlink ref="V6" r:id="rId29"/>
-    <x:hyperlink ref="U7" r:id="rId1"/>
-    <x:hyperlink ref="V7" r:id="rId30"/>
-    <x:hyperlink ref="U8" r:id="rId9"/>
-    <x:hyperlink ref="V8" r:id="rId31"/>
-    <x:hyperlink ref="U9" r:id="rId26"/>
-    <x:hyperlink ref="V9" r:id="rId32"/>
-    <x:hyperlink ref="U10" r:id="rId27"/>
-    <x:hyperlink ref="V10" r:id="rId33"/>
-    <x:hyperlink ref="U11" r:id="rId6"/>
-    <x:hyperlink ref="V11" r:id="rId34"/>
-    <x:hyperlink ref="U12" r:id="rId15"/>
-    <x:hyperlink ref="V12" r:id="rId35"/>
-    <x:hyperlink ref="U13" r:id="rId13"/>
-    <x:hyperlink ref="V13" r:id="rId36"/>
-    <x:hyperlink ref="U14" r:id="rId7"/>
-    <x:hyperlink ref="V14" r:id="rId37"/>
-    <x:hyperlink ref="U15" r:id="rId3"/>
-    <x:hyperlink ref="V15" r:id="rId38"/>
-    <x:hyperlink ref="U16" r:id="rId14"/>
-    <x:hyperlink ref="V16" r:id="rId39"/>
-    <x:hyperlink ref="U17" r:id="rId18"/>
-    <x:hyperlink ref="V17" r:id="rId40"/>
-    <x:hyperlink ref="U18" r:id="rId19"/>
-    <x:hyperlink ref="V18" r:id="rId41"/>
-    <x:hyperlink ref="U19" r:id="rId20"/>
-    <x:hyperlink ref="V19" r:id="rId42"/>
-    <x:hyperlink ref="U20" r:id="rId10"/>
-    <x:hyperlink ref="V20" r:id="rId43"/>
-    <x:hyperlink ref="U21" r:id="rId21"/>
-    <x:hyperlink ref="V21" r:id="rId44"/>
-    <x:hyperlink ref="U22" r:id="rId25"/>
-    <x:hyperlink ref="V22" r:id="rId45"/>
-    <x:hyperlink ref="U23" r:id="rId16"/>
-    <x:hyperlink ref="V23" r:id="rId46"/>
-    <x:hyperlink ref="U24" r:id="rId24"/>
-    <x:hyperlink ref="V24" r:id="rId47"/>
-    <x:hyperlink ref="U25" r:id="rId22"/>
-    <x:hyperlink ref="V25" r:id="rId48"/>
-    <x:hyperlink ref="U26" r:id="rId5"/>
-    <x:hyperlink ref="V26" r:id="rId49"/>
-    <x:hyperlink ref="U27" r:id="rId17"/>
-    <x:hyperlink ref="V27" r:id="rId50"/>
-    <x:hyperlink ref="U28" r:id="rId8"/>
-    <x:hyperlink ref="V28" r:id="rId51"/>
-    <x:hyperlink ref="U29" r:id="rId11"/>
-    <x:hyperlink ref="V29" r:id="rId52"/>
-    <x:hyperlink ref="U30" r:id="rId12"/>
-    <x:hyperlink ref="V30" r:id="rId53"/>
-    <x:hyperlink ref="U31" r:id="rId23"/>
-    <x:hyperlink ref="V31" r:id="rId54"/>
-    <x:hyperlink ref="U32" r:id="rId77"/>
-    <x:hyperlink ref="V32" r:id="rId79"/>
-    <x:hyperlink ref="U33" r:id="rId78"/>
-    <x:hyperlink ref="V33" r:id="rId80"/>
-    <x:hyperlink ref="U34" r:id="rId76"/>
-    <x:hyperlink ref="V34" r:id="rId81"/>
-    <x:hyperlink ref="U35" r:id="rId75"/>
-    <x:hyperlink ref="V35" r:id="rId82"/>
-    <x:hyperlink ref="U36" r:id="rId83"/>
-    <x:hyperlink ref="V36" r:id="rId97"/>
-    <x:hyperlink ref="U37" r:id="rId87"/>
-    <x:hyperlink ref="V37" r:id="rId98"/>
-    <x:hyperlink ref="U38" r:id="rId84"/>
-    <x:hyperlink ref="V38" r:id="rId99"/>
-    <x:hyperlink ref="U39" r:id="rId85"/>
-    <x:hyperlink ref="V39" r:id="rId100"/>
-    <x:hyperlink ref="U40" r:id="rId86"/>
-    <x:hyperlink ref="V40" r:id="rId101"/>
-    <x:hyperlink ref="U41" r:id="rId88"/>
-    <x:hyperlink ref="V41" r:id="rId102"/>
-    <x:hyperlink ref="U42" r:id="rId90"/>
-    <x:hyperlink ref="V42" r:id="rId103"/>
-    <x:hyperlink ref="U43" r:id="rId96"/>
-    <x:hyperlink ref="V43" r:id="rId104"/>
-    <x:hyperlink ref="U44" r:id="rId92"/>
-    <x:hyperlink ref="V44" r:id="rId105"/>
-    <x:hyperlink ref="U45" r:id="rId93"/>
-    <x:hyperlink ref="V45" r:id="rId106"/>
-    <x:hyperlink ref="U46" r:id="rId95"/>
-    <x:hyperlink ref="V46" r:id="rId107"/>
-    <x:hyperlink ref="U47" r:id="rId94"/>
-    <x:hyperlink ref="V47" r:id="rId108"/>
-    <x:hyperlink ref="U48" r:id="rId91"/>
-    <x:hyperlink ref="V48" r:id="rId109"/>
-    <x:hyperlink ref="U49" r:id="rId89"/>
-    <x:hyperlink ref="V49" r:id="rId110"/>
-    <x:hyperlink ref="U50" r:id="rId69"/>
-    <x:hyperlink ref="V50" r:id="rId72"/>
-    <x:hyperlink ref="U51" r:id="rId71"/>
-    <x:hyperlink ref="V51" r:id="rId73"/>
-    <x:hyperlink ref="U52" r:id="rId70"/>
-    <x:hyperlink ref="V52" r:id="rId74"/>
-    <x:hyperlink ref="U53" r:id="rId55"/>
-    <x:hyperlink ref="V53" r:id="rId57"/>
-    <x:hyperlink ref="U54" r:id="rId56"/>
-    <x:hyperlink ref="V54" r:id="rId58"/>
-    <x:hyperlink ref="U55" r:id="rId59"/>
-    <x:hyperlink ref="V55" r:id="rId64"/>
-    <x:hyperlink ref="U56" r:id="rId60"/>
-    <x:hyperlink ref="V56" r:id="rId65"/>
-    <x:hyperlink ref="U57" r:id="rId62"/>
-    <x:hyperlink ref="V57" r:id="rId66"/>
-    <x:hyperlink ref="U58" r:id="rId63"/>
-    <x:hyperlink ref="V58" r:id="rId67"/>
-    <x:hyperlink ref="U59" r:id="rId61"/>
-    <x:hyperlink ref="V59" r:id="rId68"/>
+    <x:hyperlink ref="U5" r:id="rIdHyperlink1"/>
+    <x:hyperlink ref="V5" r:id="rIdHyperlink2"/>
+    <x:hyperlink ref="U6" r:id="rIdHyperlink3"/>
+    <x:hyperlink ref="V6" r:id="rIdHyperlink4"/>
+    <x:hyperlink ref="U7" r:id="rIdHyperlink5"/>
+    <x:hyperlink ref="V7" r:id="rIdHyperlink6"/>
+    <x:hyperlink ref="U8" r:id="rIdHyperlink7"/>
+    <x:hyperlink ref="V8" r:id="rIdHyperlink8"/>
+    <x:hyperlink ref="U9" r:id="rIdHyperlink9"/>
+    <x:hyperlink ref="V9" r:id="rIdHyperlink10"/>
+    <x:hyperlink ref="U10" r:id="rIdHyperlink11"/>
+    <x:hyperlink ref="V10" r:id="rIdHyperlink12"/>
+    <x:hyperlink ref="U11" r:id="rIdHyperlink13"/>
+    <x:hyperlink ref="V11" r:id="rIdHyperlink14"/>
+    <x:hyperlink ref="U12" r:id="rIdHyperlink15"/>
+    <x:hyperlink ref="V12" r:id="rIdHyperlink16"/>
+    <x:hyperlink ref="U13" r:id="rIdHyperlink17"/>
+    <x:hyperlink ref="V13" r:id="rIdHyperlink18"/>
+    <x:hyperlink ref="U14" r:id="rIdHyperlink19"/>
+    <x:hyperlink ref="V14" r:id="rIdHyperlink20"/>
+    <x:hyperlink ref="U15" r:id="rIdHyperlink21"/>
+    <x:hyperlink ref="V15" r:id="rIdHyperlink22"/>
+    <x:hyperlink ref="U16" r:id="rIdHyperlink23"/>
+    <x:hyperlink ref="V16" r:id="rIdHyperlink24"/>
+    <x:hyperlink ref="U17" r:id="rIdHyperlink25"/>
+    <x:hyperlink ref="V17" r:id="rIdHyperlink26"/>
+    <x:hyperlink ref="U18" r:id="rIdHyperlink27"/>
+    <x:hyperlink ref="V18" r:id="rIdHyperlink28"/>
+    <x:hyperlink ref="U19" r:id="rIdHyperlink29"/>
+    <x:hyperlink ref="V19" r:id="rIdHyperlink30"/>
+    <x:hyperlink ref="U20" r:id="rIdHyperlink31"/>
+    <x:hyperlink ref="V20" r:id="rIdHyperlink32"/>
+    <x:hyperlink ref="U21" r:id="rIdHyperlink33"/>
+    <x:hyperlink ref="V21" r:id="rIdHyperlink34"/>
+    <x:hyperlink ref="U22" r:id="rIdHyperlink35"/>
+    <x:hyperlink ref="V22" r:id="rIdHyperlink36"/>
+    <x:hyperlink ref="U23" r:id="rIdHyperlink37"/>
+    <x:hyperlink ref="V23" r:id="rIdHyperlink38"/>
+    <x:hyperlink ref="U24" r:id="rIdHyperlink39"/>
+    <x:hyperlink ref="V24" r:id="rIdHyperlink40"/>
+    <x:hyperlink ref="U25" r:id="rIdHyperlink41"/>
+    <x:hyperlink ref="V25" r:id="rIdHyperlink42"/>
+    <x:hyperlink ref="U26" r:id="rIdHyperlink43"/>
+    <x:hyperlink ref="V26" r:id="rIdHyperlink44"/>
+    <x:hyperlink ref="U27" r:id="rIdHyperlink45"/>
+    <x:hyperlink ref="V27" r:id="rIdHyperlink46"/>
+    <x:hyperlink ref="U28" r:id="rIdHyperlink47"/>
+    <x:hyperlink ref="V28" r:id="rIdHyperlink48"/>
+    <x:hyperlink ref="U29" r:id="rIdHyperlink49"/>
+    <x:hyperlink ref="V29" r:id="rIdHyperlink50"/>
+    <x:hyperlink ref="U30" r:id="rIdHyperlink51"/>
+    <x:hyperlink ref="V30" r:id="rIdHyperlink52"/>
+    <x:hyperlink ref="U31" r:id="rIdHyperlink53"/>
+    <x:hyperlink ref="V31" r:id="rIdHyperlink54"/>
+    <x:hyperlink ref="U32" r:id="rIdHyperlink55"/>
+    <x:hyperlink ref="V32" r:id="rIdHyperlink56"/>
+    <x:hyperlink ref="U33" r:id="rIdHyperlink57"/>
+    <x:hyperlink ref="V33" r:id="rIdHyperlink58"/>
+    <x:hyperlink ref="U34" r:id="rIdHyperlink59"/>
+    <x:hyperlink ref="V34" r:id="rIdHyperlink60"/>
+    <x:hyperlink ref="U35" r:id="rIdHyperlink61"/>
+    <x:hyperlink ref="V35" r:id="rIdHyperlink62"/>
+    <x:hyperlink ref="U36" r:id="rIdHyperlink63"/>
+    <x:hyperlink ref="V36" r:id="rIdHyperlink64"/>
+    <x:hyperlink ref="U37" r:id="rIdHyperlink65"/>
+    <x:hyperlink ref="V37" r:id="rIdHyperlink66"/>
+    <x:hyperlink ref="U38" r:id="rIdHyperlink67"/>
+    <x:hyperlink ref="V38" r:id="rIdHyperlink68"/>
+    <x:hyperlink ref="U39" r:id="rIdHyperlink69"/>
+    <x:hyperlink ref="V39" r:id="rIdHyperlink70"/>
+    <x:hyperlink ref="U40" r:id="rIdHyperlink71"/>
+    <x:hyperlink ref="V40" r:id="rIdHyperlink72"/>
+    <x:hyperlink ref="U41" r:id="rIdHyperlink73"/>
+    <x:hyperlink ref="V41" r:id="rIdHyperlink74"/>
+    <x:hyperlink ref="U42" r:id="rIdHyperlink75"/>
+    <x:hyperlink ref="V42" r:id="rIdHyperlink76"/>
+    <x:hyperlink ref="U43" r:id="rIdHyperlink77"/>
+    <x:hyperlink ref="V43" r:id="rIdHyperlink78"/>
+    <x:hyperlink ref="U44" r:id="rIdHyperlink79"/>
+    <x:hyperlink ref="V44" r:id="rIdHyperlink80"/>
+    <x:hyperlink ref="U45" r:id="rIdHyperlink81"/>
+    <x:hyperlink ref="V45" r:id="rIdHyperlink82"/>
+    <x:hyperlink ref="U46" r:id="rIdHyperlink83"/>
+    <x:hyperlink ref="V46" r:id="rIdHyperlink84"/>
+    <x:hyperlink ref="U47" r:id="rIdHyperlink85"/>
+    <x:hyperlink ref="V47" r:id="rIdHyperlink86"/>
+    <x:hyperlink ref="U48" r:id="rIdHyperlink87"/>
+    <x:hyperlink ref="V48" r:id="rIdHyperlink88"/>
+    <x:hyperlink ref="U49" r:id="rIdHyperlink89"/>
+    <x:hyperlink ref="V49" r:id="rIdHyperlink90"/>
+    <x:hyperlink ref="U50" r:id="rIdHyperlink91"/>
+    <x:hyperlink ref="V50" r:id="rIdHyperlink92"/>
+    <x:hyperlink ref="U51" r:id="rIdHyperlink93"/>
+    <x:hyperlink ref="V51" r:id="rIdHyperlink94"/>
+    <x:hyperlink ref="U52" r:id="rIdHyperlink95"/>
+    <x:hyperlink ref="V52" r:id="rIdHyperlink96"/>
+    <x:hyperlink ref="U53" r:id="rIdHyperlink97"/>
+    <x:hyperlink ref="V53" r:id="rIdHyperlink98"/>
+    <x:hyperlink ref="U54" r:id="rIdHyperlink99"/>
+    <x:hyperlink ref="V54" r:id="rIdHyperlink100"/>
+    <x:hyperlink ref="U55" r:id="rIdHyperlink101"/>
+    <x:hyperlink ref="V55" r:id="rIdHyperlink102"/>
+    <x:hyperlink ref="U56" r:id="rIdHyperlink103"/>
+    <x:hyperlink ref="V56" r:id="rIdHyperlink104"/>
+    <x:hyperlink ref="U57" r:id="rIdHyperlink105"/>
+    <x:hyperlink ref="V57" r:id="rIdHyperlink106"/>
+    <x:hyperlink ref="U58" r:id="rIdHyperlink107"/>
+    <x:hyperlink ref="V58" r:id="rIdHyperlink108"/>
+    <x:hyperlink ref="U59" r:id="rIdHyperlink109"/>
+    <x:hyperlink ref="V59" r:id="rIdHyperlink110"/>
   </x:hyperlinks>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId111"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a5c3514a66f4d2b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5436,15 +5436,15 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:hyperlinks>
-    <x:hyperlink ref="B5" r:id="rId1"/>
-    <x:hyperlink ref="B6" r:id="rId2"/>
-    <x:hyperlink ref="B7" r:id="rId3"/>
-    <x:hyperlink ref="B8" r:id="rId4"/>
-    <x:hyperlink ref="B9" r:id="rId5"/>
-    <x:hyperlink ref="B10" r:id="rId6"/>
+    <x:hyperlink ref="B5" r:id="rIdHyperlink1"/>
+    <x:hyperlink ref="B6" r:id="rIdHyperlink2"/>
+    <x:hyperlink ref="B7" r:id="rIdHyperlink3"/>
+    <x:hyperlink ref="B8" r:id="rIdHyperlink4"/>
+    <x:hyperlink ref="B9" r:id="rIdHyperlink5"/>
+    <x:hyperlink ref="B10" r:id="rIdHyperlink6"/>
   </x:hyperlinks>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9991fadafa90478b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/05_交付物/通俗细分版_2026-08-07/05_编程数学数据分析和可视化/00_大分类总览.xlsx
+++ b/05_交付物/通俗细分版_2026-08-07/05_编程数学数据分析和可视化/00_大分类总览.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R491eb27989c7499a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI技能清单" sheetId="2" r:id="R2d7b08b6edb94cbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类统计" sheetId="3" r:id="R7d4dad11b55b42d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源清单" sheetId="4" r:id="R39604f80ebe24654"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R5528fa2d6e664b78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI技能清单" sheetId="2" r:id="Rc12e980c1d13430a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类统计" sheetId="3" r:id="Rbf0f4dedf7ba470b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源清单" sheetId="4" r:id="R167017d9f98945af"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4796,7 +4796,7 @@
     <x:hyperlink ref="V59" r:id="rIdHyperlink110"/>
   </x:hyperlinks>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a5c3514a66f4d2b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e7203cb8e7b43de"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5444,7 +5444,7 @@
     <x:hyperlink ref="B10" r:id="rIdHyperlink6"/>
   </x:hyperlinks>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9991fadafa90478b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94492a1834014689"/>
   </x:tableParts>
 </x:worksheet>
 </file>